--- a/Intersecciones/excels/SAN_MARTIN-RIOJA-RIOJA.xlsx
+++ b/Intersecciones/excels/SAN_MARTIN-RIOJA-RIOJA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-341623</t>
+          <t>I-530523</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-6.0558961</t>
+          <t>-6.0170423</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-77.166831</t>
+          <t>-77.2540929</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-341676</t>
+          <t>I-530524</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,22 +560,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-6.0638026</t>
+          <t>-6.0580103</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-77.1713225</t>
+          <t>-77.2538005</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-341685</t>
+          <t>I-530521</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -612,25 +612,1169 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>-6.0160297</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-77.2535838</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>I-18781</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>220804</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NUEVA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-5.9193886</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-77.2948781</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Carretera San Fernando / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>I-644124</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>220804</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NUEVA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-5.910031</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-77.3162533</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>I-644125</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>220804</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NUEVA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-5.9108749</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-77.3180017</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>I-644126</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>220804</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NUEVA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-5.9115047</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-77.3192747</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>I-341676</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-6.0638026</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-77.1713225</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-341685</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>-6.0668682</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>-77.168703</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>I-419192</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-6.0600439</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-77.1721516</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>I-419364</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-6.0547663</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-77.172688</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>I-556317</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-6.0642839</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-77.1835987</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>I-531586</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-5.9890687</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-77.2151756</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>I-531588</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-5.9909117</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-77.2154658</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>I-531589</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-5.9900014</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-77.2153501</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>I-531590</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-5.9918215</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-77.2156164</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>I-556283</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-6.0767292</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-77.1707109</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>I-556285</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-6.0738687</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-77.1712817</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>I-556289</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-6.0769237</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-77.1688188</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>I-556290</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-6.0768309</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-77.1697214</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>I-419401</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-6.064765</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-77.1823613</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>I-556309</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-6.0683477</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-77.1813437</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>I-556314</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-6.0684302</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-77.184307</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>I-556316</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-6.0698995</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-77.18162</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>I-556320</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-6.0660828</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-77.1797251</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>220801</t>
         </is>

--- a/Intersecciones/excels/SAN_MARTIN-RIOJA-RIOJA.xlsx
+++ b/Intersecciones/excels/SAN_MARTIN-RIOJA-RIOJA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1780,6 +1780,318 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>I-17000</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-5.9891951</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-77.2142357</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>I-556312</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-6.0681221</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-77.1832333</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>I-556299</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-6.0754575</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-77.1688168</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>I-556300</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-6.0759711</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-77.1650458</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>I-556301</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-6.0746005</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-77.1685216</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>I-18782</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>220804</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>NUEVA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-5.9310941</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-77.3105079</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Carretera San Fernando / Jirón Francisco</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/SAN_MARTIN-RIOJA-RIOJA.xlsx
+++ b/Intersecciones/excels/SAN_MARTIN-RIOJA-RIOJA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2092,6 +2092,58 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>I-18784</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>220804</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NUEVA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-5.9293203</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-77.3084667</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Carretera San Fernando / Jirón Federico Villarreal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/SAN_MARTIN-RIOJA-RIOJA.xlsx
+++ b/Intersecciones/excels/SAN_MARTIN-RIOJA-RIOJA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-530523</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-6.0170423</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-530524</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-6.0580103</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-530521</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-6.0160297</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-18781</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>220804</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>NUEVA CAJAMARCA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-5.9193886</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-644124</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>220804</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>NUEVA CAJAMARCA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-5.910031</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-644125</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>220804</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>NUEVA CAJAMARCA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-5.9108749</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-644126</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>220804</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>NUEVA CAJAMARCA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-5.9115047</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-341676</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-6.0638026</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-341685</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-6.0668682</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-419192</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-6.0600439</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-419364</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-6.0547663</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-556317</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-6.0642839</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-531586</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-5.9890687</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-531588</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-5.9909117</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-531589</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-5.9900014</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-531590</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-5.9918215</t>
@@ -1304,40 +1224,35 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>I-556283</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-6.0767292</t>
@@ -1356,40 +1271,35 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>I-556285</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-6.0738687</t>
@@ -1408,40 +1318,35 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>I-556289</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-6.0769237</t>
@@ -1460,40 +1365,35 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>I-556290</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-6.0768309</t>
@@ -1512,40 +1412,35 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>I-419401</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-6.064765</t>
@@ -1564,40 +1459,35 @@
       <c r="I22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>I-556309</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-6.0683477</t>
@@ -1616,40 +1506,35 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>I-556314</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-6.0684302</t>
@@ -1668,40 +1553,35 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>I-556316</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-6.0698995</t>
@@ -1720,40 +1600,35 @@
       <c r="I25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>I-556320</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-6.0660828</t>
@@ -1772,40 +1647,35 @@
       <c r="I26" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>I-17000</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-5.9891951</t>
@@ -1824,40 +1694,35 @@
       <c r="I27" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>I-556312</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>-6.0681221</t>
@@ -1876,40 +1741,35 @@
       <c r="I28" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>I-556299</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>-6.0754575</t>
@@ -1928,40 +1788,35 @@
       <c r="I29" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>I-556300</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>-6.0759711</t>
@@ -1980,40 +1835,35 @@
       <c r="I30" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>I-556301</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>220801</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>-6.0746005</t>
@@ -2032,40 +1882,35 @@
       <c r="I31" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>I-18782</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>220804</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>NUEVA CAJAMARCA</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>-5.9310941</t>
@@ -2084,40 +1929,35 @@
       <c r="I32" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>I-18784</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>220804</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>RIOJA</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>NUEVA CAJAMARCA</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>-5.9293203</t>
@@ -2136,11 +1976,6 @@
       <c r="I33" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>220801</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/SAN_MARTIN-RIOJA-RIOJA.xlsx
+++ b/Intersecciones/excels/SAN_MARTIN-RIOJA-RIOJA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/SAN_MARTIN-RIOJA-RIOJA.xlsx
+++ b/Intersecciones/excels/SAN_MARTIN-RIOJA-RIOJA.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">

--- a/Intersecciones/excels/SAN_MARTIN-RIOJA-RIOJA.xlsx
+++ b/Intersecciones/excels/SAN_MARTIN-RIOJA-RIOJA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,51 +413,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>
@@ -1974,6 +1962,288 @@
         </is>
       </c>
       <c r="I33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>I-341601</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-6.0595708</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-77.1635136</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>av. Santa rosa cruce con jr. Raymondi</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>I-341642</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-6.0608841</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-77.1691062</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>jr. Libertad cruce con jr. Iquitos</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>I-341697</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-6.0663928</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-77.1652616</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>jr. Chachapoyas cruce con jr. Angaiza</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>I-341699</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-6.0658751</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-77.1630489</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>jr. Teobaldo lopez cruce con jr. Chachapoyas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>I-341700</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-6.0670016</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-77.1701667</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>jr. Chachapoyas cruce con jr. jr. Amargura</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>220801</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>RIOJA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>I-341738</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-6.0648457</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-77.167857</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>jr. San Martin cruce con jr. Tacna</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/Intersecciones/excels/SAN_MARTIN-RIOJA-RIOJA.xlsx
+++ b/Intersecciones/excels/SAN_MARTIN-RIOJA-RIOJA.xlsx
@@ -1008,17 +1008,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-6.0642839</t>
+          <t>-6.057739</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-77.1835987</t>
+          <t>-77.166265</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>JR. TEOBALDO LOPEZ CRUCE CON JR. JOSE OLAYA</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1290,17 +1290,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-6.0738687</t>
+          <t>-6.062754</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-77.1712817</t>
+          <t>-77.166262</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>DOS DE MAYO/JR. ANGAIZA</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1384,17 +1384,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-6.0768309</t>
+          <t>-6.058692</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-77.1697214</t>
+          <t>-77.170409</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>JR. JOSE OLAYA CRUCE CON JR. AYACUCHO</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-6.064765</t>
+          <t>-6.059428</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-77.1823613</t>
+          <t>-77.169145</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>JR. LIBERTAD CRUCE CON JR. CUSCO</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1525,17 +1525,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-6.0684302</t>
+          <t>-6.062384</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-77.184307</t>
+          <t>-77.170029</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>JR. MIGUEL GRAU CRUCE CON JR. BOLIVAR</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1619,17 +1619,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-6.0660828</t>
+          <t>-6.058305</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-77.1797251</t>
+          <t>-77.168347</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>JR. SANTO TORIBIO CRUCE CON JR. JOSE OLAYA</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1713,17 +1713,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-6.0681221</t>
+          <t>-6.065182</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-77.1832333</t>
+          <t>-77.164401</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>JR. COLON CRUE CON JR. BOLOGNESI</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1760,17 +1760,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-6.0754575</t>
+          <t>-6.064652</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-77.1688168</t>
+          <t>-77.165678</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>JR. ANGAIZA CRUCE CON JR. TACNA</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1854,17 +1854,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-6.0746005</t>
+          <t>-6.060922</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-77.1685216</t>
+          <t>-77.163756</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>JR. JULIO C. ARANA CRUCE CON  JR. RAYMONDI</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">

--- a/Intersecciones/excels/SAN_MARTIN-RIOJA-RIOJA.xlsx
+++ b/Intersecciones/excels/SAN_MARTIN-RIOJA-RIOJA.xlsx
@@ -486,17 +486,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-530523</t>
+          <t>I-644126</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-6.0170423</t>
+          <t>-5.9115047</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-77.2540929</t>
+          <t>-77.3192747</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -533,17 +533,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-530524</t>
+          <t>I-644125</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-6.0580103</t>
+          <t>-5.9108749</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-77.2538005</t>
+          <t>-77.3180017</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -580,17 +580,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-530521</t>
+          <t>I-644124</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-6.0160297</t>
+          <t>-5.910031</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-77.2535838</t>
+          <t>-77.3162533</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-18781</t>
+          <t>I-556320</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-5.9193886</t>
+          <t>-6.058305</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-77.2948781</t>
+          <t>-77.168347</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Carretera San Fernando / Calle s / n</t>
+          <t>JR. SANTO TORIBIO CRUCE CON JR. JOSE OLAYA</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-644124</t>
+          <t>I-556317</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-5.910031</t>
+          <t>-6.057739</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-77.3162533</t>
+          <t>-77.166265</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>JR. TEOBALDO LOPEZ CRUCE CON JR. JOSE OLAYA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -721,17 +721,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-644125</t>
+          <t>I-556316</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-5.9108749</t>
+          <t>-6.0698995</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-77.3180017</t>
+          <t>-77.18162</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-644126</t>
+          <t>I-556314</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-5.9115047</t>
+          <t>-6.062384</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-77.3192747</t>
+          <t>-77.170029</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>JR. MIGUEL GRAU CRUCE CON JR. BOLIVAR</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -815,27 +815,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-341676</t>
+          <t>I-556312</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-6.0638026</t>
+          <t>-6.065182</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-77.1713225</t>
+          <t>-77.164401</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>JR. COLON CRUE CON JR. BOLOGNESI</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-341685</t>
+          <t>I-556309</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-6.0668682</t>
+          <t>-6.0683477</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-77.168703</t>
+          <t>-77.1813437</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -909,22 +909,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-419192</t>
+          <t>I-556301</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-6.0600439</t>
+          <t>-6.060922</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-77.1721516</t>
+          <t>-77.163756</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>JR. JULIO C. ARANA CRUCE CON  JR. RAYMONDI</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-419364</t>
+          <t>I-556300</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-6.0547663</t>
+          <t>-6.0759711</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-77.172688</t>
+          <t>-77.1650458</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1003,22 +1003,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-556317</t>
+          <t>I-556299</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-6.057739</t>
+          <t>-6.064652</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-77.166265</t>
+          <t>-77.165678</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>JR. TEOBALDO LOPEZ CRUCE CON JR. JOSE OLAYA</t>
+          <t>JR. ANGAIZA CRUCE CON JR. TACNA</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1050,22 +1050,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-531586</t>
+          <t>I-556290</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-5.9890687</t>
+          <t>-6.058692</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-77.2151756</t>
+          <t>-77.170409</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>JR. JOSE OLAYA CRUCE CON JR. AYACUCHO</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-531588</t>
+          <t>I-556289</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-5.9909117</t>
+          <t>-6.0769237</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-77.2154658</t>
+          <t>-77.1688188</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1144,22 +1144,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-531589</t>
+          <t>I-556285</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-5.9900014</t>
+          <t>-6.062754</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-77.2153501</t>
+          <t>-77.166262</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>DOS DE MAYO/JR. ANGAIZA</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1191,17 +1191,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-531590</t>
+          <t>I-556283</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-5.9918215</t>
+          <t>-6.0767292</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-77.2156164</t>
+          <t>-77.1707109</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1238,17 +1238,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-556283</t>
+          <t>I-531590</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-6.0767292</t>
+          <t>-5.9918215</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-77.1707109</t>
+          <t>-77.2156164</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1285,22 +1285,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-556285</t>
+          <t>I-531589</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-6.062754</t>
+          <t>-5.9900014</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-77.166262</t>
+          <t>-77.2153501</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DOS DE MAYO/JR. ANGAIZA</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1332,17 +1332,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-556289</t>
+          <t>I-531588</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-6.0769237</t>
+          <t>-5.9909117</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-77.1688188</t>
+          <t>-77.2154658</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1379,22 +1379,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-556290</t>
+          <t>I-531586</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-6.058692</t>
+          <t>-5.9890687</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-77.170409</t>
+          <t>-77.2151756</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>JR. JOSE OLAYA CRUCE CON JR. AYACUCHO</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-419401</t>
+          <t>I-530524</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-6.059428</t>
+          <t>-6.0580103</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-77.169145</t>
+          <t>-77.2538005</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>JR. LIBERTAD CRUCE CON JR. CUSCO</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-556309</t>
+          <t>I-530523</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-6.0683477</t>
+          <t>-6.0170423</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-77.1813437</t>
+          <t>-77.2540929</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1520,22 +1520,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I-556314</t>
+          <t>I-530521</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-6.062384</t>
+          <t>-6.0160297</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-77.170029</t>
+          <t>-77.2535838</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>JR. MIGUEL GRAU CRUCE CON JR. BOLIVAR</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1567,22 +1567,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I-556316</t>
+          <t>I-419401</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-6.0698995</t>
+          <t>-6.059428</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-77.18162</t>
+          <t>-77.169145</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>JR. LIBERTAD CRUCE CON JR. CUSCO</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1614,22 +1614,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I-556320</t>
+          <t>I-419364</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-6.058305</t>
+          <t>-6.0547663</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-77.168347</t>
+          <t>-77.172688</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>JR. SANTO TORIBIO CRUCE CON JR. JOSE OLAYA</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>I-17000</t>
+          <t>I-419192</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-5.9891951</t>
+          <t>-6.0600439</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-77.2142357</t>
+          <t>-77.1721516</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>I-556312</t>
+          <t>I-341738</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-6.065182</t>
+          <t>-6.0648457</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-77.164401</t>
+          <t>-77.167857</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>JR. COLON CRUE CON JR. BOLOGNESI</t>
+          <t>jr. San Martin cruce con jr. Tacna</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1755,22 +1755,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>I-556299</t>
+          <t>I-341700</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-6.064652</t>
+          <t>-6.0670016</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-77.165678</t>
+          <t>-77.1701667</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>JR. ANGAIZA CRUCE CON JR. TACNA</t>
+          <t>jr. Chachapoyas cruce con jr. jr. Amargura</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>I-556300</t>
+          <t>I-341699</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-6.0759711</t>
+          <t>-6.0658751</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-77.1650458</t>
+          <t>-77.1630489</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>jr. Teobaldo lopez cruce con jr. Chachapoyas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1849,22 +1849,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>I-556301</t>
+          <t>I-341697</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-6.060922</t>
+          <t>-6.0663928</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-77.163756</t>
+          <t>-77.1652616</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>JR. JULIO C. ARANA CRUCE CON  JR. RAYMONDI</t>
+          <t>jr. Chachapoyas cruce con jr. Angaiza</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1896,27 +1896,27 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>I-18782</t>
+          <t>I-341685</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-5.9310941</t>
+          <t>-6.0668682</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-77.3105079</t>
+          <t>-77.168703</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Carretera San Fernando / Jirón Francisco</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1943,27 +1943,27 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>I-18784</t>
+          <t>I-341676</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-5.9293203</t>
+          <t>-6.0638026</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-77.3084667</t>
+          <t>-77.1713225</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Carretera San Fernando / Jirón Federico Villarreal</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1990,22 +1990,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>I-341601</t>
+          <t>I-341642</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-6.0595708</t>
+          <t>-6.0608841</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-77.1635136</t>
+          <t>-77.1691062</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>av. Santa rosa cruce con jr. Raymondi</t>
+          <t>jr. Libertad cruce con jr. Iquitos</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>I-341642</t>
+          <t>I-341601</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-6.0608841</t>
+          <t>-6.0595708</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-77.1691062</t>
+          <t>-77.1635136</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>jr. Libertad cruce con jr. Iquitos</t>
+          <t>av. Santa rosa cruce con jr. Raymondi</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2084,22 +2084,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>I-341697</t>
+          <t>I-18784</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-6.0663928</t>
+          <t>-5.9293203</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-77.1652616</t>
+          <t>-77.3084667</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>jr. Chachapoyas cruce con jr. Angaiza</t>
+          <t>Carretera San Fernando / Jirón Federico Villarreal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2131,22 +2131,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>I-341699</t>
+          <t>I-18782</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-6.0658751</t>
+          <t>-5.9310941</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-77.1630489</t>
+          <t>-77.3105079</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>jr. Teobaldo lopez cruce con jr. Chachapoyas</t>
+          <t>Carretera San Fernando / Jirón Francisco</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2178,22 +2178,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>I-341700</t>
+          <t>I-18781</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-6.0670016</t>
+          <t>-5.9193886</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-77.1701667</t>
+          <t>-77.2948781</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>jr. Chachapoyas cruce con jr. jr. Amargura</t>
+          <t>Carretera San Fernando / Calle s / n</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2225,22 +2225,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>I-341738</t>
+          <t>I-17000</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-6.0648457</t>
+          <t>-5.9891951</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-77.167857</t>
+          <t>-77.2142357</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>jr. San Martin cruce con jr. Tacna</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
